--- a/etf_holdings/2026-10-25_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-25_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-25 21:22:17</t>
+          <t>2026-10-25 21:43:21</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-25 21:22:17</t>
+          <t>2026-10-25 21:43:21</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25 21:22:17</t>
+          <t>2026-10-25 21:43:21</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-25 21:22:17</t>
+          <t>2026-10-25 21:43:21</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-25 21:22:17</t>
+          <t>2026-10-25 21:43:21</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-25 21:22:17</t>
+          <t>2026-10-25 21:43:21</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-25 21:22:17</t>
+          <t>2026-10-25 21:43:21</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-25 21:22:17</t>
+          <t>2026-10-25 21:43:21</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-25 21:22:17</t>
+          <t>2026-10-25 21:43:21</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-25 21:22:17</t>
+          <t>2026-10-25 21:43:21</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-25 21:22:17</t>
+          <t>2026-10-25 21:43:21</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-25 21:22:17</t>
+          <t>2026-10-25 21:43:21</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-25 21:22:17</t>
+          <t>2026-10-25 21:43:21</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-25 21:22:17</t>
+          <t>2026-10-25 21:43:21</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-25 21:22:17</t>
+          <t>2026-10-25 21:43:21</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
